--- a/docs/control-plane/06_DEPLOYMENT_RELEASE_REGISTRY.xlsx
+++ b/docs/control-plane/06_DEPLOYMENT_RELEASE_REGISTRY.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="106">
   <si>
     <t>06_DEPLOYMENT_RELEASE_REGISTRY</t>
   </si>
@@ -46,6 +46,12 @@
     <t>CRITICAL: NEVER STORE PASSWORDS, API KEYS, SERVICE-ROLE KEYS, PRIVATE CERTIFICATES, SMTP PASSWORDS, OR R2 SECRETS IN THIS WORKBOOK. USE SECURE ENVIRONMENT REFERENCES ONLY.</t>
   </si>
   <si>
+    <t>Canonical Production Subdomain</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in (Parent domain: arivahly.in)</t>
+  </si>
+  <si>
     <t>AI Operating Constraint 1</t>
   </si>
   <si>
@@ -70,10 +76,16 @@
     <t>UNKNOWN means unknown. Do not guess. If a field is uncertain, record NEEDS_VERIFICATION.</t>
   </si>
   <si>
+    <t>MCP Security Boundary</t>
+  </si>
+  <si>
+    <t>MCP is DISABLED and BLOCKED from public routing. MCP tools must remain internal/local only.</t>
+  </si>
+  <si>
     <t>Last Audit Date</t>
   </si>
   <si>
-    <t>2026-09-05T13:10:00+05:30 (Release v1.1.2-online-production-hardened)</t>
+    <t>2026-09-05T13:20:00+05:30 (Release v1.1.2-online-production-hardened)</t>
   </si>
   <si>
     <t>Deployment_ID</t>
@@ -139,19 +151,19 @@
     <t>feature/production-v1.1.2</t>
   </si>
   <si>
-    <t>bf0c7c75043b13fcb10b112ed981ef54a39f44f0</t>
+    <t>HEAD</t>
   </si>
   <si>
     <t>v1.1.2-online-production-hardened</t>
   </si>
   <si>
-    <t>PASSED (13.54s build)</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>DEPLOYED</t>
   </si>
   <si>
-    <t>maatarajewellers.shop</t>
+    <t>erp.arivahly.in</t>
   </si>
   <si>
     <t>Supabase PostgreSQL (RLS Active)</t>
@@ -163,7 +175,7 @@
     <t>Proxied / WAF Active</t>
   </si>
   <si>
-    <t>2026-09-05 13:10</t>
+    <t>2026-09-05 13:20</t>
   </si>
   <si>
     <t>Aritra Manna</t>
@@ -172,7 +184,7 @@
     <t>ACTIVE</t>
   </si>
   <si>
-    <t>Final online managed SaaS release with full hardening and edge protection</t>
+    <t>Final online managed SaaS release with full hardening and edge protection on https://erp.arivahly.in</t>
   </si>
   <si>
     <t>Release_ID</t>
@@ -220,9 +232,6 @@
     <t>REL-PROD-V1.1.2</t>
   </si>
   <si>
-    <t>PASSED</t>
-  </si>
-  <si>
     <t>PASSED (RLS)</t>
   </si>
   <si>
@@ -253,7 +262,7 @@
     <t>PASSED (WAF/AI Block)</t>
   </si>
   <si>
-    <t>PASSED (HTTPS)</t>
+    <t>PASSED (HTTPS: erp.arivahly.in)</t>
   </si>
   <si>
     <t>PASSED (Zero Leaks)</t>
@@ -304,13 +313,13 @@
     <t>2026-09-05</t>
   </si>
   <si>
-    <t>https://maatarajewellers.shop</t>
-  </si>
-  <si>
-    <t>https://maatarajewellers.shop/api/health.php</t>
-  </si>
-  <si>
-    <t>https://maatarajewellers.shop/verify/invoice/:token</t>
+    <t>https://erp.arivahly.in</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in/api/health.php</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in/verify/invoice/:token</t>
   </si>
   <si>
     <t>YES (57 files / 437 tests)</t>
@@ -322,7 +331,7 @@
     <t>RELEASED</t>
   </si>
   <si>
-    <t>Production certified online managed release</t>
+    <t>Production certified online managed release on erp.arivahly.in</t>
   </si>
 </sst>
 </file>
@@ -770,7 +779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -855,6 +864,22 @@
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -872,11 +897,11 @@
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="44" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
+    <col min="9" max="9" width="19" customWidth="1"/>
     <col min="10" max="10" width="36" customWidth="1"/>
     <col min="11" max="11" width="33" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
@@ -888,108 +913,108 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>47</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="P2" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1017,7 +1042,7 @@
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="25" customWidth="1"/>
-    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="15" max="15" width="35" customWidth="1"/>
     <col min="16" max="16" width="23" customWidth="1"/>
     <col min="17" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="39" customWidth="1"/>
@@ -1025,120 +1050,120 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="R2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S2" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1153,113 +1178,112 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="3" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="37" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="33" customWidth="1"/>
-    <col min="8" max="8" width="48" customWidth="1"/>
-    <col min="9" max="9" width="54" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
+    <col min="9" max="9" width="49" customWidth="1"/>
     <col min="10" max="10" width="23" customWidth="1"/>
     <col min="11" max="11" width="30" customWidth="1"/>
     <col min="12" max="12" width="24" customWidth="1"/>
     <col min="13" max="13" width="16" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
-    <col min="15" max="15" width="47" customWidth="1"/>
+    <col min="15" max="15" width="54" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" s="6" t="s">
-        <v>101</v>
+        <v>54</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/docs/control-plane/06_DEPLOYMENT_RELEASE_REGISTRY.xlsx
+++ b/docs/control-plane/06_DEPLOYMENT_RELEASE_REGISTRY.xlsx
@@ -151,7 +151,7 @@
     <t>feature/production-v1.1.2</t>
   </si>
   <si>
-    <t>HEAD</t>
+    <t>4f1c5da05d4b88705182c31a44c4d5b768dead50</t>
   </si>
   <si>
     <t>v1.1.2-online-production-hardened</t>
@@ -897,7 +897,7 @@
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="23" customWidth="1"/>
     <col min="4" max="4" width="29" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="5" max="5" width="44" customWidth="1"/>
     <col min="6" max="6" width="37" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
@@ -1178,7 +1178,8 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="19" customWidth="1"/>
-    <col min="3" max="4" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="37" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="27" customWidth="1"/>
